--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
@@ -377,10 +377,10 @@
         <v>920.64</v>
       </c>
       <c r="B2">
-        <v>908.846</v>
+        <v>908.573</v>
       </c>
       <c r="C2">
-        <v>932.239</v>
+        <v>932.39</v>
       </c>
     </row>
   </sheetData>
@@ -415,10 +415,10 @@
         <v>949.657</v>
       </c>
       <c r="B2">
-        <v>937.534</v>
+        <v>937.4160000000001</v>
       </c>
       <c r="C2">
-        <v>962.237</v>
+        <v>962.28</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
@@ -374,13 +374,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>920.64</v>
+        <v>890.601</v>
       </c>
       <c r="B2">
-        <v>908.573</v>
+        <v>875.522</v>
       </c>
       <c r="C2">
-        <v>932.39</v>
+        <v>905.886</v>
       </c>
     </row>
   </sheetData>
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>949.657</v>
+        <v>928.737</v>
       </c>
       <c r="B2">
-        <v>937.4160000000001</v>
+        <v>913.984</v>
       </c>
       <c r="C2">
-        <v>962.28</v>
+        <v>943.721</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
@@ -374,13 +374,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>890.601</v>
+        <v>829.7569999999999</v>
       </c>
       <c r="B2">
-        <v>875.522</v>
+        <v>816.167</v>
       </c>
       <c r="C2">
-        <v>905.886</v>
+        <v>843.524</v>
       </c>
     </row>
   </sheetData>
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>928.737</v>
+        <v>865.287</v>
       </c>
       <c r="B2">
-        <v>913.984</v>
+        <v>851.992</v>
       </c>
       <c r="C2">
-        <v>943.721</v>
+        <v>878.574</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
@@ -374,13 +374,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>829.7569999999999</v>
+        <v>913.633</v>
       </c>
       <c r="B2">
-        <v>816.167</v>
+        <v>901.534</v>
       </c>
       <c r="C2">
-        <v>843.524</v>
+        <v>925.905</v>
       </c>
     </row>
   </sheetData>
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>865.287</v>
+        <v>939.099</v>
       </c>
       <c r="B2">
-        <v>851.992</v>
+        <v>926.865</v>
       </c>
       <c r="C2">
-        <v>878.574</v>
+        <v>951.13</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted_Boot.xlsx
@@ -374,13 +374,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>913.633</v>
+        <v>3944.396</v>
       </c>
       <c r="B2">
-        <v>901.534</v>
+        <v>3889.136</v>
       </c>
       <c r="C2">
-        <v>925.905</v>
+        <v>4001.247</v>
       </c>
     </row>
   </sheetData>
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>939.099</v>
+        <v>3598.473</v>
       </c>
       <c r="B2">
-        <v>926.865</v>
+        <v>3546.557</v>
       </c>
       <c r="C2">
-        <v>951.13</v>
+        <v>3647.878</v>
       </c>
     </row>
   </sheetData>
